--- a/openspec/題庫_11508.xlsx
+++ b/openspec/題庫_11508.xlsx
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="H14" t="str">
-        <v>番薯機|馬鈴薯機+夯番麥:2|熱狗機|蒸包機|蛋鍋（不足1/2；麻辣蛋不觀察）|馬尚煮機|備品區（醬包、袋子、熱狗麵包…）|炸烤物櫃|現烤點心櫃|其他:填寫</v>
+        <v>番薯機|馬鈴薯機+夯番麥|熱狗機|蒸包機|蛋鍋（不足1/2；麻辣蛋不觀察）|馬尚煮機|備品區（醬包、袋子…）|炸烤物櫃|現烤點心櫃|其他:填寫</v>
       </c>
       <c r="I14" t="str">
         <v>商品、醬包、備品陳列整齊不可空架</v>
